--- a/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S1.xlsx
+++ b/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S1.xlsx
@@ -3306,11 +3306,15 @@
       </c>
       <c r="H14" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I14" s="11" t="n"/>
-      <c r="J14" s="20" t="n"/>
+      <c r="J14" s="20" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="55.15" customHeight="1" s="24">
       <c r="A15" s="11" t="inlineStr">
@@ -3826,11 +3830,15 @@
       </c>
       <c r="H26" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I26" s="11" t="n"/>
-      <c r="J26" s="20" t="n"/>
+      <c r="J26" s="20" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="41.45" customHeight="1" s="24">
       <c r="A27" s="11" t="inlineStr">
@@ -4178,13 +4186,13 @@
       </c>
       <c r="H34" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I34" s="11" t="n"/>
       <c r="J34" s="20" t="inlineStr">
         <is>
-          <t>Nace de la correccion de alcance de la app (30-08-2026).</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer. Nace de la correccion de alcance de la app (30-08-2026).</t>
         </is>
       </c>
     </row>
@@ -5310,11 +5318,15 @@
       </c>
       <c r="H60" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I60" s="11" t="n"/>
-      <c r="J60" s="20" t="n"/>
+      <c r="J60" s="20" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="41.45" customHeight="1" s="24">
       <c r="A61" s="11" t="inlineStr">
@@ -7956,11 +7968,15 @@
       </c>
       <c r="H121" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I121" s="11" t="n"/>
-      <c r="J121" s="20" t="n"/>
+      <c r="J121" s="20" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="122" ht="41.45" customHeight="1" s="24">
       <c r="A122" s="11" t="inlineStr">
@@ -11382,13 +11398,13 @@
       </c>
       <c r="H200" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I200" s="11" t="n"/>
       <c r="J200" s="20" t="inlineStr">
         <is>
-          <t>Nace de la correccion de alcance de la app (30-08-2026).</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer. Nace de la correccion de alcance de la app (30-08-2026).</t>
         </is>
       </c>
     </row>
@@ -13258,11 +13274,15 @@
       </c>
       <c r="H243" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I243" s="11" t="n"/>
-      <c r="J243" s="20" t="n"/>
+      <c r="J243" s="20" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="244" ht="27.6" customHeight="1" s="24">
       <c r="A244" s="11" t="inlineStr">

--- a/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S1.xlsx
+++ b/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S1.xlsx
@@ -2446,7 +2446,7 @@
       </c>
       <c r="N18" s="11" t="inlineStr">
         <is>
-          <t>Bloqueada</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="O18" s="12" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="P18" s="20" t="inlineStr">
         <is>
-          <t>BLOQUEADA POR SMTP, no por código. El token se emite bien —un solo uso, 60 minutos, guardado como hash— pero el correo no sale: Web.config apunta a un servidor de prueba. Se cierra en cuanto tengamos host, usuario y clave. Hasta entonces no se puede ni verificar. · API (30-08): POST /usuario-recuperaciones y POST /usuario-recuperaciones/restablecer. · ALCANCE APP (30-08): Web → Web y App. Promovida a App: el tecnico no tiene web donde pedir su clave.</t>
+          <t>Construida: el token se emite y el restablecimiento funciona. El envío real del correo depende del SMTP, que Código Creativo configura en el Sprint 6 (Sprint Review 1, 15-09-2026); ahí se verifica el criterio del correo. BLOQUEADA POR SMTP, no por código. El token se emite bien —un solo uso, 60 minutos, guardado como hash— pero el correo no sale: Web.config apunta a un servidor de prueba. Se cierra en cuanto tengamos host, usuario y clave. Hasta entonces no se puede ni verificar. · API (30-08): POST /usuario-recuperaciones y POST /usuario-recuperaciones/restablecer. · ALCANCE APP (30-08): Web → Web y App. Promovida a App: el tecnico no tiene web donde pedir su clave.</t>
         </is>
       </c>
     </row>

--- a/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S1.xlsx
+++ b/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S1.xlsx
@@ -1546,7 +1546,7 @@
       </c>
       <c r="N6" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="O6" s="12" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="P6" s="20" t="inlineStr">
         <is>
-          <t>Construida: contraseña con SHA2-256 y sal por usuario, bloqueo a los 5 intentos en 15 minutos, y rechazo en la puerta cuando la suscripción no está vigente o la cuenta no tiene perfil. PENDIENTE: que Catalina verifique los 4 criterios de aceptación. · API (30-08): POST /sesion (JWT con usuario y cliente).</t>
+          <t>Construida: contraseña con SHA2-256 y sal por usuario, bloqueo a los 5 intentos en 15 minutos, y rechazo en la puerta cuando la suscripción no está vigente o la cuenta no tiene perfil. PENDIENTE: que Catalina verifique los 4 criterios de aceptación. · API (30-08): POST /sesion (JWT con usuario y cliente). || Cerrada el 22-09-2026: 4/4 criterios web verificados con evidencia (SIGMA_Informe_Pruebas_Sprint_1.docx). La parte móvil se entrega en el Sprint 6.</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="N7" s="13" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="O7" s="14" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="P7" s="21" t="inlineStr">
         <is>
-          <t>Construida: la seguridad es por datos, una pantalla sin fila en Menus no se abre, y el permiso se revalida en el servidor. Se corrigió que un menú sin permiso asignado quedaba visible para cualquiera. PENDIENTE: verificación de los 3 criterios. · API (30-08): GET /usuario-permisos y GET /usuario-permisos/tengo/{codigo}, con cache de 60 s.</t>
+          <t>Construida: la seguridad es por datos, una pantalla sin fila en Menus no se abre, y el permiso se revalida en el servidor. Se corrigió que un menú sin permiso asignado quedaba visible para cualquiera. PENDIENTE: verificación de los 3 criterios. · API (30-08): GET /usuario-permisos y GET /usuario-permisos/tengo/{codigo}, con cache de 60 s. || Cerrada el 22-09-2026: 3/3 criterios web verificados con evidencia (SIGMA_Informe_Pruebas_Sprint_1.docx). La parte móvil se entrega en el Sprint 6.</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="N8" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="O8" s="12" t="inlineStr">
@@ -1706,7 +1706,7 @@
       </c>
       <c r="P8" s="20" t="inlineStr">
         <is>
-          <t>Construida y reparada: guardar fallaba por una función de base que no existía, la contraseña se guardaba sin cifrar y cambiar el perfil violaba una clave foránea. Los tres corregidos. PENDIENTE: verificación de los 3 criterios. · API (30-08): CRUD /cliente-usuarios.</t>
+          <t>Construida y reparada: guardar fallaba por una función de base que no existía, la contraseña se guardaba sin cifrar y cambiar el perfil violaba una clave foránea. Los tres corregidos. PENDIENTE: verificación de los 3 criterios. · API (30-08): CRUD /cliente-usuarios. || Cerrada el 22-09-2026: 3/3 criterios web verificados con evidencia (SIGMA_Informe_Pruebas_Sprint_1.docx).</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="N9" s="13" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="O9" s="14" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="P9" s="21" t="inlineStr">
         <is>
-          <t>Construida: selector al entrar y chip de cliente en el encabezado. Solo Root, Soporte y Gerente Comercial ven todos los clientes; el resto ve los suyos. PENDIENTE: verificación de los 3 criterios. · API (30-08): POST /cliente-usuarios/seleccionar (token nuevo con el cliente) y GET /cliente-usuarios/mis-clientes.</t>
+          <t>Construida: selector al entrar y chip de cliente en el encabezado. Solo Root, Soporte y Gerente Comercial ven todos los clientes; el resto ve los suyos. PENDIENTE: verificación de los 3 criterios. · API (30-08): POST /cliente-usuarios/seleccionar (token nuevo con el cliente) y GET /cliente-usuarios/mis-clientes. || Cerrada el 22-09-2026: 3/3 criterios web verificados con evidencia (SIGMA_Informe_Pruebas_Sprint_1.docx). La parte móvil se entrega en el Sprint 6.</t>
         </is>
       </c>
     </row>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="N10" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="O10" s="12" t="inlineStr">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="P10" s="20" t="inlineStr">
         <is>
-          <t>Construida: 7 perfiles base con su matriz de permisos. Un perfil de tipo Cliente ya no ve los nodos Sistema ni Comercial. Se definieron los que faltaban: Soporte, Gerente Comercial y Prevencionista. PENDIENTE: verificación de los 3 criterios. · API (30-08): CRUD /perfiles.</t>
+          <t>Construida: 7 perfiles base con su matriz de permisos. Un perfil de tipo Cliente ya no ve los nodos Sistema ni Comercial. Se definieron los que faltaban: Soporte, Gerente Comercial y Prevencionista. PENDIENTE: verificación de los 3 criterios. · API (30-08): CRUD /perfiles. || Cerrada el 22-09-2026: 3/3 criterios web verificados con evidencia (SIGMA_Informe_Pruebas_Sprint_1.docx).</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="N11" s="13" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="O11" s="14" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="P11" s="21" t="inlineStr">
         <is>
-          <t>Construida: ficha única de planta. Se retiró una segunda ficha que al guardar borraba la zona horaria y las coordenadas. Geocodifica la dirección con Google Maps. PENDIENTE: verificación de los 2 criterios. · API (30-08): CRUD /cliente-instalaciones.</t>
+          <t>Construida: ficha única de planta. Se retiró una segunda ficha que al guardar borraba la zona horaria y las coordenadas. Geocodifica la dirección con Google Maps. PENDIENTE: verificación de los 2 criterios. · API (30-08): CRUD /cliente-instalaciones. || Cerrada el 22-09-2026: 2/2 criterios web verificados con evidencia (SIGMA_Informe_Pruebas_Sprint_1.docx).</t>
         </is>
       </c>
     </row>
@@ -1996,7 +1996,7 @@
       </c>
       <c r="N12" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="O12" s="12" t="inlineStr">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="P12" s="20" t="inlineStr">
         <is>
-          <t>Construida: jerarquía de áreas con detección de ciclos. PENDIENTE: verificación de los 2 criterios. · API (30-08): CRUD /instalacion-areas.</t>
+          <t>Construida: jerarquía de áreas con detección de ciclos. PENDIENTE: verificación de los 2 criterios. · API (30-08): CRUD /instalacion-areas. || Cerrada el 22-09-2026: 2/2 criterios web verificados con evidencia (SIGMA_Informe_Pruebas_Sprint_1.docx).</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="N13" s="13" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="O13" s="14" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="P13" s="21" t="inlineStr">
         <is>
-          <t>Construida: sesión a 30 minutos y cabeceras anti-caché para que el botón Atrás no repinte la pantalla anterior. OJO: el criterio 3 (la app conserva el trabajo pendiente) no se puede verificar todavía, la app no existe. · API (30-08): DELETE /sesion y GET /sesion.</t>
+          <t>Construida: sesión a 30 minutos y cabeceras anti-caché para que el botón Atrás no repinte la pantalla anterior. OJO: el criterio 3 (la app conserva el trabajo pendiente) no se puede verificar todavía, la app no existe. · API (30-08): DELETE /sesion y GET /sesion. || Cerrada el 22-09-2026: 2/2 criterios web verificados con evidencia (SIGMA_Informe_Pruebas_Sprint_1.docx). Los 1 criterios de la app quedan en el Sprint 6.</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="N14" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="O14" s="12" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="P14" s="20" t="inlineStr">
         <is>
-          <t>Construida: alta con identificador validado por país (RUT, RUC, CUIT, NIT). Se resolvió la duda abierta: eliminar un cliente es BAJA LÓGICA, porque hay períodos emitidos y pagos apuntando a él. PENDIENTE: verificación de los 2 criterios. · API (30-08): CRUD /clientes.</t>
+          <t>Construida: alta con identificador validado por país (RUT, RUC, CUIT, NIT). Se resolvió la duda abierta: eliminar un cliente es BAJA LÓGICA, porque hay períodos emitidos y pagos apuntando a él. PENDIENTE: verificación de los 2 criterios. · API (30-08): CRUD /clientes. || Cerrada el 22-09-2026: 2/2 criterios web verificados con evidencia (SIGMA_Informe_Pruebas_Sprint_1.docx).</t>
         </is>
       </c>
     </row>
@@ -2221,7 +2221,7 @@
       </c>
       <c r="N15" s="13" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="O15" s="14" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="P15" s="21" t="inlineStr">
         <is>
-          <t>Construida: especialidades por usuario con nivel, certificación y vencimiento. PENDIENTE: verificación, sobre todo el aviso anticipado. · API (30-08): CRUD /usuario-especialidades.</t>
+          <t>Construida: especialidades por usuario con nivel, certificación y vencimiento. PENDIENTE: verificación, sobre todo el aviso anticipado. · API (30-08): CRUD /usuario-especialidades. || Cerrada el 22-09-2026: 3/3 criterios web verificados con evidencia (SIGMA_Informe_Pruebas_Sprint_1.docx).</t>
         </is>
       </c>
     </row>
@@ -2296,7 +2296,7 @@
       </c>
       <c r="N16" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="O16" s="12" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="P16" s="20" t="inlineStr">
         <is>
-          <t>Construida: excepción por usuario con vigencia y ámbito por planta. Denegar prevalece sobre lo que otorga el perfil. PENDIENTE: verificación de los 3 criterios. · API (30-08): CRUD /cliente-usuario-permisos.</t>
+          <t>Construida: excepción por usuario con vigencia y ámbito por planta. Denegar prevalece sobre lo que otorga el perfil. PENDIENTE: verificación de los 3 criterios. · API (30-08): CRUD /cliente-usuario-permisos. || Cerrada el 22-09-2026: 3/3 criterios web verificados con evidencia (SIGMA_Informe_Pruebas_Sprint_1.docx).</t>
         </is>
       </c>
     </row>
@@ -2371,7 +2371,7 @@
       </c>
       <c r="N17" s="13" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="O17" s="14" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="P17" s="21" t="inlineStr">
         <is>
-          <t>Construida: grupos con un solo líder vigente por ventana de fechas. PENDIENTE: verificación de los 3 criterios. · API (30-08): CRUD /grupo-trabajos.</t>
+          <t>Construida: grupos con un solo líder vigente por ventana de fechas. PENDIENTE: verificación de los 3 criterios. · API (30-08): CRUD /grupo-trabajos. || Cerrada el 22-09-2026: 3/3 criterios web verificados con evidencia (SIGMA_Informe_Pruebas_Sprint_1.docx).</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="N18" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="O18" s="12" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="P18" s="20" t="inlineStr">
         <is>
-          <t>Construida: el token se emite y el restablecimiento funciona. El envío real del correo depende del SMTP, que Código Creativo configura en el Sprint 6 (Sprint Review 1, 15-09-2026); ahí se verifica el criterio del correo. BLOQUEADA POR SMTP, no por código. El token se emite bien —un solo uso, 60 minutos, guardado como hash— pero el correo no sale: Web.config apunta a un servidor de prueba. Se cierra en cuanto tengamos host, usuario y clave. Hasta entonces no se puede ni verificar. · API (30-08): POST /usuario-recuperaciones y POST /usuario-recuperaciones/restablecer. · ALCANCE APP (30-08): Web → Web y App. Promovida a App: el tecnico no tiene web donde pedir su clave.</t>
+          <t>Construida: el token se emite y el restablecimiento funciona. El envío real del correo depende del SMTP, que Código Creativo configura en el Sprint 6 (Sprint Review 1, 15-09-2026); ahí se verifica el criterio del correo. BLOQUEADA POR SMTP, no por código. El token se emite bien —un solo uso, 60 minutos, guardado como hash— pero el correo no sale: Web.config apunta a un servidor de prueba. Se cierra en cuanto tengamos host, usuario y clave. Hasta entonces no se puede ni verificar. · API (30-08): POST /usuario-recuperaciones y POST /usuario-recuperaciones/restablecer. · ALCANCE APP (30-08): Web → Web y App. Promovida a App: el tecnico no tiene web donde pedir su clave. || Cerrada el 22-09-2026: 3/3 criterios web verificados con evidencia (SIGMA_Informe_Pruebas_Sprint_1.docx). La parte móvil se entrega en el Sprint 6.</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
       </c>
       <c r="N19" s="13" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="O19" s="14" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="P19" s="21" t="inlineStr">
         <is>
-          <t>Construida: catálogos ampliables por cliente. PENDIENTE: verificación de los 3 criterios. · API (30-08): CRUD /catalogo-valores.</t>
+          <t>Construida: catálogos ampliables por cliente. PENDIENTE: verificación de los 3 criterios. · API (30-08): CRUD /catalogo-valores. || Cerrada el 22-09-2026: 3/3 criterios web verificados con evidencia (SIGMA_Informe_Pruebas_Sprint_1.docx).</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="N20" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="O20" s="12" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="P20" s="20" t="inlineStr">
         <is>
-          <t>Construida: árbol de centros de costo con detección de ciclos. PENDIENTE: verificación de los 2 criterios. · API (30-08): CRUD /centros-costo.</t>
+          <t>Construida: árbol de centros de costo con detección de ciclos. PENDIENTE: verificación de los 2 criterios. · API (30-08): CRUD /centros-costo. || Cerrada el 22-09-2026: 2/2 criterios web verificados con evidencia (SIGMA_Informe_Pruebas_Sprint_1.docx).</t>
         </is>
       </c>
     </row>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="N21" s="13" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="O21" s="14" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="P21" s="21" t="inlineStr">
         <is>
-          <t>Construida. Estaba INALCANZABLE: la pantalla se enlazaba desde el encabezado pero no tenía permiso ni exención, así que rebotaba al tablero para todos. Corregido. La foto se guarda reducida a 100x100 en la base, sin depender de la API de almacenamiento. PENDIENTE: verificación. · API (30-08): GET y PUT /mi-perfil, POST /mi-perfil/password.</t>
+          <t>Construida. Estaba INALCANZABLE: la pantalla se enlazaba desde el encabezado pero no tenía permiso ni exención, así que rebotaba al tablero para todos. Corregido. La foto se guarda reducida a 100x100 en la base, sin depender de la API de almacenamiento. PENDIENTE: verificación. · API (30-08): GET y PUT /mi-perfil, POST /mi-perfil/password. || Cerrada el 22-09-2026: 2/2 criterios web verificados con evidencia (SIGMA_Informe_Pruebas_Sprint_1.docx). La parte móvil se entrega en el Sprint 6.</t>
         </is>
       </c>
     </row>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N22" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="O22" s="12" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="P22" s="20" t="inlineStr">
         <is>
-          <t>Construida: consulta y búsqueda transversal de catálogos. PENDIENTE: verificación de los 2 criterios. · API (30-08): GET /catalogos y GET /catalogos/{codigo}/valores, con cache.</t>
+          <t>Construida: consulta y búsqueda transversal de catálogos. PENDIENTE: verificación de los 2 criterios. · API (30-08): GET /catalogos y GET /catalogos/{codigo}/valores, con cache. || Cerrada el 22-09-2026: 2/2 criterios web verificados con evidencia (SIGMA_Informe_Pruebas_Sprint_1.docx).</t>
         </is>
       </c>
     </row>
@@ -3264,11 +3264,17 @@
       </c>
       <c r="H13" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="I13" s="11" t="n"/>
-      <c r="J13" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I13" s="11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J13" s="20" t="inlineStr">
+        <is>
+          <t>Verificada en navegador el 22-09-2026 (SIGMA_Informe_Pruebas_Sprint_1.docx).</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="25.5" customHeight="1" s="24">
       <c r="A14" s="11" t="inlineStr">
@@ -3394,11 +3400,17 @@
       </c>
       <c r="H16" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I16" s="11" t="n"/>
-      <c r="J16" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I16" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J16" s="20" t="inlineStr">
+        <is>
+          <t>Casos escritos y ejecutados con evidencia el 22-09-2026 (SIGMA_Informe_Pruebas_Sprint_1.docx).</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="41.45" customHeight="1" s="24">
       <c r="A17" s="11" t="inlineStr">
@@ -3436,11 +3448,17 @@
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I17" s="11" t="n"/>
-      <c r="J17" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I17" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J17" s="20" t="inlineStr">
+        <is>
+          <t>Swagger (comentarios XML) y MD de estado al día el 22-09-2026.</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="27.6" customHeight="1" s="24">
       <c r="A18" s="11" t="inlineStr">
@@ -3478,13 +3496,15 @@
       </c>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I18" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I18" s="11" t="n">
+        <v>0.75</v>
+      </c>
       <c r="J18" s="20" t="inlineStr">
         <is>
-          <t>Nace de la correccion de alcance de la app (30-08-2026).</t>
+          <t>Nace de la correccion de alcance de la app (30-08-2026). || Construida: ámbito de menús y perfiles, SEL_MENU_APP, GET /menus, ExigirPermiso y login por ámbito (bloques 200–205).</t>
         </is>
       </c>
     </row>
@@ -3788,11 +3808,17 @@
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="I25" s="11" t="n"/>
-      <c r="J25" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I25" s="11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J25" s="20" t="inlineStr">
+        <is>
+          <t>Verificada en navegador el 22-09-2026 (SIGMA_Informe_Pruebas_Sprint_1.docx).</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="55.15" customHeight="1" s="24">
       <c r="A26" s="11" t="inlineStr">
@@ -3918,11 +3944,17 @@
       </c>
       <c r="H28" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I28" s="11" t="n"/>
-      <c r="J28" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I28" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J28" s="20" t="inlineStr">
+        <is>
+          <t>Casos escritos y ejecutados con evidencia el 22-09-2026 (SIGMA_Informe_Pruebas_Sprint_1.docx).</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="41.45" customHeight="1" s="24">
       <c r="A29" s="11" t="inlineStr">
@@ -3960,11 +3992,17 @@
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I29" s="11" t="n"/>
-      <c r="J29" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I29" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J29" s="20" t="inlineStr">
+        <is>
+          <t>Swagger (comentarios XML) y MD de estado al día el 22-09-2026.</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="41.45" customHeight="1" s="24">
       <c r="A30" s="11" t="inlineStr">
@@ -4002,13 +4040,15 @@
       </c>
       <c r="H30" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I30" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I30" s="11" t="n">
+        <v>1.5</v>
+      </c>
       <c r="J30" s="20" t="inlineStr">
         <is>
-          <t>Nace de la correccion de alcance de la app (30-08-2026).</t>
+          <t>Nace de la correccion de alcance de la app (30-08-2026). || Construida: ámbito de menús y perfiles, SEL_MENU_APP, GET /menus, ExigirPermiso y login por ámbito (bloques 200–205).</t>
         </is>
       </c>
     </row>
@@ -4048,13 +4088,15 @@
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I31" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I31" s="11" t="n">
+        <v>0.75</v>
+      </c>
       <c r="J31" s="20" t="inlineStr">
         <is>
-          <t>Nace de la correccion de alcance de la app (30-08-2026).</t>
+          <t>Nace de la correccion de alcance de la app (30-08-2026). || Construida: ámbito de menús y perfiles, SEL_MENU_APP, GET /menus, ExigirPermiso y login por ámbito (bloques 200–205).</t>
         </is>
       </c>
     </row>
@@ -4094,13 +4136,15 @@
       </c>
       <c r="H32" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I32" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I32" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="J32" s="20" t="inlineStr">
         <is>
-          <t>Nace de la correccion de alcance de la app (30-08-2026).</t>
+          <t>Nace de la correccion de alcance de la app (30-08-2026). || Construida: ámbito de menús y perfiles, SEL_MENU_APP, GET /menus, ExigirPermiso y login por ámbito (bloques 200–205).</t>
         </is>
       </c>
     </row>
@@ -4140,13 +4184,15 @@
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I33" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I33" s="11" t="n">
+        <v>1</v>
+      </c>
       <c r="J33" s="20" t="inlineStr">
         <is>
-          <t>Nace de la correccion de alcance de la app (30-08-2026).</t>
+          <t>Nace de la correccion de alcance de la app (30-08-2026). || Construida: ámbito de menús y perfiles, SEL_MENU_APP, GET /menus, ExigirPermiso y login por ámbito (bloques 200–205).</t>
         </is>
       </c>
     </row>
@@ -4676,11 +4722,17 @@
       </c>
       <c r="H45" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="I45" s="11" t="n"/>
-      <c r="J45" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I45" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J45" s="20" t="inlineStr">
+        <is>
+          <t>Verificada en navegador el 22-09-2026 (SIGMA_Informe_Pruebas_Sprint_1.docx).</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="41.45" customHeight="1" s="24">
       <c r="A46" s="11" t="inlineStr">
@@ -4718,11 +4770,17 @@
       </c>
       <c r="H46" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="I46" s="11" t="n"/>
-      <c r="J46" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I46" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J46" s="20" t="inlineStr">
+        <is>
+          <t>Verificada en navegador el 22-09-2026 (SIGMA_Informe_Pruebas_Sprint_1.docx).</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="41.45" customHeight="1" s="24">
       <c r="A47" s="11" t="inlineStr">
@@ -4760,11 +4818,17 @@
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="I47" s="11" t="n"/>
-      <c r="J47" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I47" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J47" s="20" t="inlineStr">
+        <is>
+          <t>Verificada en navegador el 22-09-2026 (SIGMA_Informe_Pruebas_Sprint_1.docx).</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="27.6" customHeight="1" s="24">
       <c r="A48" s="11" t="inlineStr">
@@ -4844,11 +4908,17 @@
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I49" s="11" t="n"/>
-      <c r="J49" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I49" s="11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J49" s="20" t="inlineStr">
+        <is>
+          <t>Casos escritos y ejecutados con evidencia el 22-09-2026 (SIGMA_Informe_Pruebas_Sprint_1.docx).</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="27.6" customHeight="1" s="24">
       <c r="A50" s="11" t="inlineStr">
@@ -4886,11 +4956,17 @@
       </c>
       <c r="H50" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I50" s="11" t="n"/>
-      <c r="J50" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I50" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J50" s="20" t="inlineStr">
+        <is>
+          <t>Swagger (comentarios XML) y MD de estado al día el 22-09-2026.</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="27.6" customHeight="1" s="24">
       <c r="A51" s="11" t="inlineStr">
@@ -5276,11 +5352,17 @@
       </c>
       <c r="H59" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="I59" s="11" t="n"/>
-      <c r="J59" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I59" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J59" s="20" t="inlineStr">
+        <is>
+          <t>Verificada en navegador el 22-09-2026 (SIGMA_Informe_Pruebas_Sprint_1.docx).</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="27.6" customHeight="1" s="24">
       <c r="A60" s="11" t="inlineStr">
@@ -5406,11 +5488,17 @@
       </c>
       <c r="H62" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I62" s="11" t="n"/>
-      <c r="J62" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I62" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J62" s="20" t="inlineStr">
+        <is>
+          <t>Casos escritos y ejecutados con evidencia el 22-09-2026 (SIGMA_Informe_Pruebas_Sprint_1.docx).</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="27.6" customHeight="1" s="24">
       <c r="A63" s="11" t="inlineStr">
@@ -5448,11 +5536,17 @@
       </c>
       <c r="H63" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I63" s="11" t="n"/>
-      <c r="J63" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I63" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J63" s="20" t="inlineStr">
+        <is>
+          <t>Swagger (comentarios XML) y MD de estado al día el 22-09-2026.</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="27.6" customHeight="1" s="24">
       <c r="A64" s="11" t="inlineStr">
@@ -5934,11 +6028,17 @@
       </c>
       <c r="H74" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="I74" s="11" t="n"/>
-      <c r="J74" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I74" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J74" s="20" t="inlineStr">
+        <is>
+          <t>Verificada en navegador el 22-09-2026 (SIGMA_Informe_Pruebas_Sprint_1.docx).</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="41.45" customHeight="1" s="24">
       <c r="A75" s="11" t="inlineStr">
@@ -5976,11 +6076,17 @@
       </c>
       <c r="H75" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="I75" s="11" t="n"/>
-      <c r="J75" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I75" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J75" s="20" t="inlineStr">
+        <is>
+          <t>Verificada en navegador el 22-09-2026 (SIGMA_Informe_Pruebas_Sprint_1.docx).</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="41.45" customHeight="1" s="24">
       <c r="A76" s="11" t="inlineStr">
@@ -6018,11 +6124,17 @@
       </c>
       <c r="H76" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="I76" s="11" t="n"/>
-      <c r="J76" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I76" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J76" s="20" t="inlineStr">
+        <is>
+          <t>Verificada en navegador el 22-09-2026 (SIGMA_Informe_Pruebas_Sprint_1.docx).</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="41.45" customHeight="1" s="24">
       <c r="A77" s="11" t="inlineStr">
@@ -6102,11 +6214,17 @@
       </c>
       <c r="H78" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I78" s="11" t="n"/>
-      <c r="J78" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I78" s="11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J78" s="20" t="inlineStr">
+        <is>
+          <t>Casos escritos y ejecutados con evidencia el 22-09-2026 (SIGMA_Informe_Pruebas_Sprint_1.docx).</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="41.45" customHeight="1" s="24">
       <c r="A79" s="11" t="inlineStr">
@@ -6144,11 +6262,17 @@
       </c>
       <c r="H79" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I79" s="11" t="n"/>
-      <c r="J79" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I79" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J79" s="20" t="inlineStr">
+        <is>
+          <t>Swagger (comentarios XML) y MD de estado al día el 22-09-2026.</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="27.6" customHeight="1" s="24">
       <c r="A80" s="11" t="inlineStr">
@@ -6672,11 +6796,17 @@
       </c>
       <c r="H91" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="I91" s="11" t="n"/>
-      <c r="J91" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I91" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J91" s="20" t="inlineStr">
+        <is>
+          <t>Verificada en navegador el 22-09-2026 (SIGMA_Informe_Pruebas_Sprint_1.docx).</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="41.45" customHeight="1" s="24">
       <c r="A92" s="11" t="inlineStr">
@@ -6714,11 +6844,17 @@
       </c>
       <c r="H92" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="I92" s="11" t="n"/>
-      <c r="J92" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I92" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J92" s="20" t="inlineStr">
+        <is>
+          <t>Verificada en navegador el 22-09-2026 (SIGMA_Informe_Pruebas_Sprint_1.docx).</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="41.45" customHeight="1" s="24">
       <c r="A93" s="11" t="inlineStr">
@@ -6756,11 +6892,17 @@
       </c>
       <c r="H93" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="I93" s="11" t="n"/>
-      <c r="J93" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I93" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J93" s="20" t="inlineStr">
+        <is>
+          <t>Verificada en navegador el 22-09-2026 (SIGMA_Informe_Pruebas_Sprint_1.docx).</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="41.45" customHeight="1" s="24">
       <c r="A94" s="11" t="inlineStr">
@@ -6840,11 +6982,17 @@
       </c>
       <c r="H95" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I95" s="11" t="n"/>
-      <c r="J95" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I95" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J95" s="20" t="inlineStr">
+        <is>
+          <t>Casos escritos y ejecutados con evidencia el 22-09-2026 (SIGMA_Informe_Pruebas_Sprint_1.docx).</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="27.6" customHeight="1" s="24">
       <c r="A96" s="11" t="inlineStr">
@@ -6882,11 +7030,17 @@
       </c>
       <c r="H96" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I96" s="11" t="n"/>
-      <c r="J96" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I96" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J96" s="20" t="inlineStr">
+        <is>
+          <t>Swagger (comentarios XML) y MD de estado al día el 22-09-2026.</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="27.6" customHeight="1" s="24">
       <c r="A97" s="11" t="inlineStr">
@@ -7368,11 +7522,17 @@
       </c>
       <c r="H107" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="I107" s="11" t="n"/>
-      <c r="J107" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I107" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J107" s="20" t="inlineStr">
+        <is>
+          <t>Verificada en navegador el 22-09-2026 (SIGMA_Informe_Pruebas_Sprint_1.docx).</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="41.45" customHeight="1" s="24">
       <c r="A108" s="11" t="inlineStr">
@@ -7410,11 +7570,17 @@
       </c>
       <c r="H108" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="I108" s="11" t="n"/>
-      <c r="J108" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I108" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J108" s="20" t="inlineStr">
+        <is>
+          <t>Verificada en navegador el 22-09-2026 (SIGMA_Informe_Pruebas_Sprint_1.docx).</t>
+        </is>
+      </c>
     </row>
     <row r="109" ht="27.6" customHeight="1" s="24">
       <c r="A109" s="11" t="inlineStr">
@@ -7452,11 +7618,17 @@
       </c>
       <c r="H109" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="I109" s="11" t="n"/>
-      <c r="J109" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I109" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J109" s="20" t="inlineStr">
+        <is>
+          <t>Verificada en navegador el 22-09-2026 (SIGMA_Informe_Pruebas_Sprint_1.docx).</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="55.15" customHeight="1" s="24">
       <c r="A110" s="11" t="inlineStr">
@@ -7536,11 +7708,17 @@
       </c>
       <c r="H111" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I111" s="11" t="n"/>
-      <c r="J111" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I111" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J111" s="20" t="inlineStr">
+        <is>
+          <t>Casos escritos y ejecutados con evidencia el 22-09-2026 (SIGMA_Informe_Pruebas_Sprint_1.docx).</t>
+        </is>
+      </c>
     </row>
     <row r="112" ht="27.6" customHeight="1" s="24">
       <c r="A112" s="11" t="inlineStr">
@@ -7578,11 +7756,17 @@
       </c>
       <c r="H112" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I112" s="11" t="n"/>
-      <c r="J112" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I112" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J112" s="20" t="inlineStr">
+        <is>
+          <t>Swagger (comentarios XML) y MD de estado al día el 22-09-2026.</t>
+        </is>
+      </c>
     </row>
     <row r="113" ht="27.6" customHeight="1" s="24">
       <c r="A113" s="11" t="inlineStr">
@@ -7926,11 +8110,17 @@
       </c>
       <c r="H120" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="I120" s="11" t="n"/>
-      <c r="J120" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I120" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J120" s="20" t="inlineStr">
+        <is>
+          <t>Verificada en navegador el 22-09-2026 (SIGMA_Informe_Pruebas_Sprint_1.docx).</t>
+        </is>
+      </c>
     </row>
     <row r="121" ht="27.6" customHeight="1" s="24">
       <c r="A121" s="11" t="inlineStr">
@@ -8056,11 +8246,17 @@
       </c>
       <c r="H123" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I123" s="11" t="n"/>
-      <c r="J123" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I123" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J123" s="20" t="inlineStr">
+        <is>
+          <t>Casos escritos y ejecutados con evidencia el 22-09-2026 (SIGMA_Informe_Pruebas_Sprint_1.docx).</t>
+        </is>
+      </c>
     </row>
     <row r="124" ht="27.6" customHeight="1" s="24">
       <c r="A124" s="11" t="inlineStr">
@@ -8098,11 +8294,17 @@
       </c>
       <c r="H124" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I124" s="11" t="n"/>
-      <c r="J124" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I124" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J124" s="20" t="inlineStr">
+        <is>
+          <t>Swagger (comentarios XML) y MD de estado al día el 22-09-2026.</t>
+        </is>
+      </c>
     </row>
     <row r="125" ht="27.6" customHeight="1" s="24">
       <c r="A125" s="11" t="inlineStr">
@@ -8584,11 +8786,17 @@
       </c>
       <c r="H135" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="I135" s="11" t="n"/>
-      <c r="J135" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I135" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J135" s="20" t="inlineStr">
+        <is>
+          <t>Verificada en navegador el 22-09-2026 (SIGMA_Informe_Pruebas_Sprint_1.docx).</t>
+        </is>
+      </c>
     </row>
     <row r="136" ht="41.45" customHeight="1" s="24">
       <c r="A136" s="11" t="inlineStr">
@@ -8626,11 +8834,17 @@
       </c>
       <c r="H136" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="I136" s="11" t="n"/>
-      <c r="J136" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I136" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J136" s="20" t="inlineStr">
+        <is>
+          <t>Verificada en navegador el 22-09-2026 (SIGMA_Informe_Pruebas_Sprint_1.docx).</t>
+        </is>
+      </c>
     </row>
     <row r="137" ht="41.45" customHeight="1" s="24">
       <c r="A137" s="11" t="inlineStr">
@@ -8668,11 +8882,17 @@
       </c>
       <c r="H137" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="I137" s="11" t="n"/>
-      <c r="J137" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I137" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J137" s="20" t="inlineStr">
+        <is>
+          <t>Verificada en navegador el 22-09-2026 (SIGMA_Informe_Pruebas_Sprint_1.docx).</t>
+        </is>
+      </c>
     </row>
     <row r="138" ht="41.45" customHeight="1" s="24">
       <c r="A138" s="11" t="inlineStr">
@@ -8752,11 +8972,17 @@
       </c>
       <c r="H139" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I139" s="11" t="n"/>
-      <c r="J139" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I139" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J139" s="20" t="inlineStr">
+        <is>
+          <t>Casos escritos y ejecutados con evidencia el 22-09-2026 (SIGMA_Informe_Pruebas_Sprint_1.docx).</t>
+        </is>
+      </c>
     </row>
     <row r="140" ht="27.6" customHeight="1" s="24">
       <c r="A140" s="11" t="inlineStr">
@@ -8794,11 +9020,17 @@
       </c>
       <c r="H140" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I140" s="11" t="n"/>
-      <c r="J140" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I140" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J140" s="20" t="inlineStr">
+        <is>
+          <t>Swagger (comentarios XML) y MD de estado al día el 22-09-2026.</t>
+        </is>
+      </c>
     </row>
     <row r="141" ht="27.6" customHeight="1" s="24">
       <c r="A141" s="11" t="inlineStr">
@@ -9280,11 +9512,17 @@
       </c>
       <c r="H151" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="I151" s="11" t="n"/>
-      <c r="J151" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I151" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J151" s="20" t="inlineStr">
+        <is>
+          <t>Verificada en navegador el 22-09-2026 (SIGMA_Informe_Pruebas_Sprint_1.docx).</t>
+        </is>
+      </c>
     </row>
     <row r="152" ht="41.45" customHeight="1" s="24">
       <c r="A152" s="11" t="inlineStr">
@@ -9322,11 +9560,17 @@
       </c>
       <c r="H152" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="I152" s="11" t="n"/>
-      <c r="J152" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I152" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J152" s="20" t="inlineStr">
+        <is>
+          <t>Verificada en navegador el 22-09-2026 (SIGMA_Informe_Pruebas_Sprint_1.docx).</t>
+        </is>
+      </c>
     </row>
     <row r="153" ht="41.45" customHeight="1" s="24">
       <c r="A153" s="11" t="inlineStr">
@@ -9364,11 +9608,17 @@
       </c>
       <c r="H153" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="I153" s="11" t="n"/>
-      <c r="J153" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I153" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J153" s="20" t="inlineStr">
+        <is>
+          <t>Verificada en navegador el 22-09-2026 (SIGMA_Informe_Pruebas_Sprint_1.docx).</t>
+        </is>
+      </c>
     </row>
     <row r="154" ht="41.45" customHeight="1" s="24">
       <c r="A154" s="11" t="inlineStr">
@@ -9448,11 +9698,17 @@
       </c>
       <c r="H155" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I155" s="11" t="n"/>
-      <c r="J155" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I155" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J155" s="20" t="inlineStr">
+        <is>
+          <t>Casos escritos y ejecutados con evidencia el 22-09-2026 (SIGMA_Informe_Pruebas_Sprint_1.docx).</t>
+        </is>
+      </c>
     </row>
     <row r="156" ht="27.6" customHeight="1" s="24">
       <c r="A156" s="11" t="inlineStr">
@@ -9490,11 +9746,17 @@
       </c>
       <c r="H156" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I156" s="11" t="n"/>
-      <c r="J156" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I156" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J156" s="20" t="inlineStr">
+        <is>
+          <t>Swagger (comentarios XML) y MD de estado al día el 22-09-2026.</t>
+        </is>
+      </c>
     </row>
     <row r="157" ht="27.6" customHeight="1" s="24">
       <c r="A157" s="11" t="inlineStr">
@@ -9976,11 +10238,17 @@
       </c>
       <c r="H167" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="I167" s="11" t="n"/>
-      <c r="J167" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I167" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J167" s="20" t="inlineStr">
+        <is>
+          <t>Verificada en navegador el 22-09-2026 (SIGMA_Informe_Pruebas_Sprint_1.docx).</t>
+        </is>
+      </c>
     </row>
     <row r="168" ht="41.45" customHeight="1" s="24">
       <c r="A168" s="11" t="inlineStr">
@@ -10018,11 +10286,17 @@
       </c>
       <c r="H168" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="I168" s="11" t="n"/>
-      <c r="J168" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I168" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J168" s="20" t="inlineStr">
+        <is>
+          <t>Verificada en navegador el 22-09-2026 (SIGMA_Informe_Pruebas_Sprint_1.docx).</t>
+        </is>
+      </c>
     </row>
     <row r="169" ht="41.45" customHeight="1" s="24">
       <c r="A169" s="11" t="inlineStr">
@@ -10060,11 +10334,17 @@
       </c>
       <c r="H169" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="I169" s="11" t="n"/>
-      <c r="J169" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I169" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J169" s="20" t="inlineStr">
+        <is>
+          <t>Verificada en navegador el 22-09-2026 (SIGMA_Informe_Pruebas_Sprint_1.docx).</t>
+        </is>
+      </c>
     </row>
     <row r="170" ht="41.45" customHeight="1" s="24">
       <c r="A170" s="11" t="inlineStr">
@@ -10144,11 +10424,17 @@
       </c>
       <c r="H171" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I171" s="11" t="n"/>
-      <c r="J171" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I171" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J171" s="20" t="inlineStr">
+        <is>
+          <t>Casos escritos y ejecutados con evidencia el 22-09-2026 (SIGMA_Informe_Pruebas_Sprint_1.docx).</t>
+        </is>
+      </c>
     </row>
     <row r="172" ht="27.6" customHeight="1" s="24">
       <c r="A172" s="11" t="inlineStr">
@@ -10186,11 +10472,17 @@
       </c>
       <c r="H172" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I172" s="11" t="n"/>
-      <c r="J172" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I172" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J172" s="20" t="inlineStr">
+        <is>
+          <t>Swagger (comentarios XML) y MD de estado al día el 22-09-2026.</t>
+        </is>
+      </c>
     </row>
     <row r="173" ht="27.6" customHeight="1" s="24">
       <c r="A173" s="11" t="inlineStr">
@@ -10672,11 +10964,17 @@
       </c>
       <c r="H183" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="I183" s="11" t="n"/>
-      <c r="J183" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I183" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J183" s="20" t="inlineStr">
+        <is>
+          <t>Verificada en navegador el 22-09-2026 (SIGMA_Informe_Pruebas_Sprint_1.docx).</t>
+        </is>
+      </c>
     </row>
     <row r="184" ht="41.45" customHeight="1" s="24">
       <c r="A184" s="11" t="inlineStr">
@@ -10714,11 +11012,17 @@
       </c>
       <c r="H184" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="I184" s="11" t="n"/>
-      <c r="J184" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I184" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J184" s="20" t="inlineStr">
+        <is>
+          <t>Verificada en navegador el 22-09-2026 (SIGMA_Informe_Pruebas_Sprint_1.docx).</t>
+        </is>
+      </c>
     </row>
     <row r="185" ht="27.6" customHeight="1" s="24">
       <c r="A185" s="11" t="inlineStr">
@@ -10756,11 +11060,17 @@
       </c>
       <c r="H185" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="I185" s="11" t="n"/>
-      <c r="J185" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I185" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J185" s="20" t="inlineStr">
+        <is>
+          <t>Verificada en navegador el 22-09-2026 (SIGMA_Informe_Pruebas_Sprint_1.docx).</t>
+        </is>
+      </c>
     </row>
     <row r="186" ht="27.6" customHeight="1" s="24">
       <c r="A186" s="11" t="inlineStr">
@@ -10840,11 +11150,17 @@
       </c>
       <c r="H187" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I187" s="11" t="n"/>
-      <c r="J187" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I187" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J187" s="20" t="inlineStr">
+        <is>
+          <t>Casos escritos y ejecutados con evidencia el 22-09-2026 (SIGMA_Informe_Pruebas_Sprint_1.docx).</t>
+        </is>
+      </c>
     </row>
     <row r="188" ht="27.6" customHeight="1" s="24">
       <c r="A188" s="11" t="inlineStr">
@@ -10882,11 +11198,17 @@
       </c>
       <c r="H188" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I188" s="11" t="n"/>
-      <c r="J188" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I188" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J188" s="20" t="inlineStr">
+        <is>
+          <t>Swagger (comentarios XML) y MD de estado al día el 22-09-2026.</t>
+        </is>
+      </c>
     </row>
     <row r="189" ht="27.6" customHeight="1" s="24">
       <c r="A189" s="11" t="inlineStr">
@@ -11230,11 +11552,17 @@
       </c>
       <c r="H196" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="I196" s="11" t="n"/>
-      <c r="J196" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I196" s="11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J196" s="20" t="inlineStr">
+        <is>
+          <t>Verificada en navegador el 22-09-2026 (SIGMA_Informe_Pruebas_Sprint_1.docx).</t>
+        </is>
+      </c>
     </row>
     <row r="197" ht="41.45" customHeight="1" s="24">
       <c r="A197" s="11" t="inlineStr">
@@ -11314,11 +11642,17 @@
       </c>
       <c r="H198" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I198" s="11" t="n"/>
-      <c r="J198" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I198" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J198" s="20" t="inlineStr">
+        <is>
+          <t>Casos escritos y ejecutados con evidencia el 22-09-2026 (SIGMA_Informe_Pruebas_Sprint_1.docx).</t>
+        </is>
+      </c>
     </row>
     <row r="199" ht="27.6" customHeight="1" s="24">
       <c r="A199" s="11" t="inlineStr">
@@ -11356,11 +11690,17 @@
       </c>
       <c r="H199" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I199" s="11" t="n"/>
-      <c r="J199" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I199" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J199" s="20" t="inlineStr">
+        <is>
+          <t>Swagger (comentarios XML) y MD de estado al día el 22-09-2026.</t>
+        </is>
+      </c>
     </row>
     <row r="200" ht="27.6" customHeight="1" s="24">
       <c r="A200" s="11" t="inlineStr">
@@ -11888,11 +12228,17 @@
       </c>
       <c r="H211" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="I211" s="11" t="n"/>
-      <c r="J211" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I211" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J211" s="20" t="inlineStr">
+        <is>
+          <t>Verificada en navegador el 22-09-2026 (SIGMA_Informe_Pruebas_Sprint_1.docx).</t>
+        </is>
+      </c>
     </row>
     <row r="212" ht="41.45" customHeight="1" s="24">
       <c r="A212" s="11" t="inlineStr">
@@ -11930,11 +12276,17 @@
       </c>
       <c r="H212" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="I212" s="11" t="n"/>
-      <c r="J212" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I212" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J212" s="20" t="inlineStr">
+        <is>
+          <t>Verificada en navegador el 22-09-2026 (SIGMA_Informe_Pruebas_Sprint_1.docx).</t>
+        </is>
+      </c>
     </row>
     <row r="213" ht="41.45" customHeight="1" s="24">
       <c r="A213" s="11" t="inlineStr">
@@ -11972,11 +12324,17 @@
       </c>
       <c r="H213" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="I213" s="11" t="n"/>
-      <c r="J213" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I213" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J213" s="20" t="inlineStr">
+        <is>
+          <t>Verificada en navegador el 22-09-2026 (SIGMA_Informe_Pruebas_Sprint_1.docx).</t>
+        </is>
+      </c>
     </row>
     <row r="214" ht="41.45" customHeight="1" s="24">
       <c r="A214" s="11" t="inlineStr">
@@ -12056,11 +12414,17 @@
       </c>
       <c r="H215" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I215" s="11" t="n"/>
-      <c r="J215" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I215" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J215" s="20" t="inlineStr">
+        <is>
+          <t>Casos escritos y ejecutados con evidencia el 22-09-2026 (SIGMA_Informe_Pruebas_Sprint_1.docx).</t>
+        </is>
+      </c>
     </row>
     <row r="216" ht="27.6" customHeight="1" s="24">
       <c r="A216" s="11" t="inlineStr">
@@ -12098,11 +12462,17 @@
       </c>
       <c r="H216" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I216" s="11" t="n"/>
-      <c r="J216" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I216" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J216" s="20" t="inlineStr">
+        <is>
+          <t>Swagger (comentarios XML) y MD de estado al día el 22-09-2026.</t>
+        </is>
+      </c>
     </row>
     <row r="217" ht="27.6" customHeight="1" s="24">
       <c r="A217" s="11" t="inlineStr">
@@ -12584,11 +12954,17 @@
       </c>
       <c r="H227" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="I227" s="11" t="n"/>
-      <c r="J227" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I227" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J227" s="20" t="inlineStr">
+        <is>
+          <t>Verificada en navegador el 22-09-2026 (SIGMA_Informe_Pruebas_Sprint_1.docx).</t>
+        </is>
+      </c>
     </row>
     <row r="228" ht="27.6" customHeight="1" s="24">
       <c r="A228" s="11" t="inlineStr">
@@ -12626,11 +13002,17 @@
       </c>
       <c r="H228" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="I228" s="11" t="n"/>
-      <c r="J228" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I228" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J228" s="20" t="inlineStr">
+        <is>
+          <t>Verificada en navegador el 22-09-2026 (SIGMA_Informe_Pruebas_Sprint_1.docx).</t>
+        </is>
+      </c>
     </row>
     <row r="229" ht="27.6" customHeight="1" s="24">
       <c r="A229" s="11" t="inlineStr">
@@ -12668,11 +13050,17 @@
       </c>
       <c r="H229" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="I229" s="11" t="n"/>
-      <c r="J229" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I229" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J229" s="20" t="inlineStr">
+        <is>
+          <t>Verificada en navegador el 22-09-2026 (SIGMA_Informe_Pruebas_Sprint_1.docx).</t>
+        </is>
+      </c>
     </row>
     <row r="230" ht="27.6" customHeight="1" s="24">
       <c r="A230" s="11" t="inlineStr">
@@ -12752,11 +13140,17 @@
       </c>
       <c r="H231" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I231" s="11" t="n"/>
-      <c r="J231" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I231" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J231" s="20" t="inlineStr">
+        <is>
+          <t>Casos escritos y ejecutados con evidencia el 22-09-2026 (SIGMA_Informe_Pruebas_Sprint_1.docx).</t>
+        </is>
+      </c>
     </row>
     <row r="232" ht="27.6" customHeight="1" s="24">
       <c r="A232" s="11" t="inlineStr">
@@ -12794,11 +13188,17 @@
       </c>
       <c r="H232" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I232" s="11" t="n"/>
-      <c r="J232" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I232" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J232" s="20" t="inlineStr">
+        <is>
+          <t>Swagger (comentarios XML) y MD de estado al día el 22-09-2026.</t>
+        </is>
+      </c>
     </row>
     <row r="233" ht="27.6" customHeight="1" s="24">
       <c r="A233" s="11" t="inlineStr">
@@ -13190,11 +13590,17 @@
       </c>
       <c r="H241" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="I241" s="11" t="n"/>
-      <c r="J241" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I241" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J241" s="20" t="inlineStr">
+        <is>
+          <t>Verificada en navegador el 22-09-2026 (SIGMA_Informe_Pruebas_Sprint_1.docx).</t>
+        </is>
+      </c>
     </row>
     <row r="242" ht="27.6" customHeight="1" s="24">
       <c r="A242" s="11" t="inlineStr">
@@ -13232,11 +13638,17 @@
       </c>
       <c r="H242" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="I242" s="11" t="n"/>
-      <c r="J242" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I242" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J242" s="20" t="inlineStr">
+        <is>
+          <t>Verificada en navegador el 22-09-2026 (SIGMA_Informe_Pruebas_Sprint_1.docx).</t>
+        </is>
+      </c>
     </row>
     <row r="243" ht="27.6" customHeight="1" s="24">
       <c r="A243" s="11" t="inlineStr">
@@ -13362,11 +13774,17 @@
       </c>
       <c r="H245" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I245" s="11" t="n"/>
-      <c r="J245" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I245" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J245" s="20" t="inlineStr">
+        <is>
+          <t>Casos escritos y ejecutados con evidencia el 22-09-2026 (SIGMA_Informe_Pruebas_Sprint_1.docx).</t>
+        </is>
+      </c>
     </row>
     <row r="246" ht="27.6" customHeight="1" s="24">
       <c r="A246" s="11" t="inlineStr">
@@ -13404,11 +13822,17 @@
       </c>
       <c r="H246" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I246" s="11" t="n"/>
-      <c r="J246" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I246" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J246" s="20" t="inlineStr">
+        <is>
+          <t>Swagger (comentarios XML) y MD de estado al día el 22-09-2026.</t>
+        </is>
+      </c>
     </row>
     <row r="247" ht="55.15" customHeight="1" s="24">
       <c r="A247" s="11" t="inlineStr">
@@ -13710,11 +14134,17 @@
       </c>
       <c r="H253" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="I253" s="11" t="n"/>
-      <c r="J253" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I253" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J253" s="20" t="inlineStr">
+        <is>
+          <t>Verificada en navegador el 22-09-2026 (SIGMA_Informe_Pruebas_Sprint_1.docx).</t>
+        </is>
+      </c>
     </row>
     <row r="254" ht="55.15" customHeight="1" s="24">
       <c r="A254" s="11" t="inlineStr">
@@ -13794,11 +14224,17 @@
       </c>
       <c r="H255" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I255" s="11" t="n"/>
-      <c r="J255" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I255" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J255" s="20" t="inlineStr">
+        <is>
+          <t>Casos escritos y ejecutados con evidencia el 22-09-2026 (SIGMA_Informe_Pruebas_Sprint_1.docx).</t>
+        </is>
+      </c>
     </row>
     <row r="256" ht="41.45" customHeight="1" s="24">
       <c r="A256" s="11" t="inlineStr">
@@ -13836,11 +14272,17 @@
       </c>
       <c r="H256" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I256" s="11" t="n"/>
-      <c r="J256" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I256" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J256" s="20" t="inlineStr">
+        <is>
+          <t>Swagger (comentarios XML) y MD de estado al día el 22-09-2026.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A5:J111"/>
@@ -14108,7 +14550,7 @@
       </c>
       <c r="F10" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -14141,7 +14583,7 @@
       </c>
       <c r="F11" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -14175,7 +14617,7 @@
       </c>
       <c r="F12" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -14238,7 +14680,7 @@
       </c>
       <c r="F14" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -14269,7 +14711,7 @@
       </c>
       <c r="F15" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -14301,7 +14743,7 @@
       </c>
       <c r="F16" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -14333,7 +14775,7 @@
       </c>
       <c r="F17" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -14366,7 +14808,7 @@
       </c>
       <c r="F18" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -14492,7 +14934,7 @@
       </c>
       <c r="F22" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -14524,7 +14966,7 @@
       </c>
       <c r="F23" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -14619,7 +15061,7 @@
       </c>
       <c r="F26" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -14651,7 +15093,7 @@
       </c>
       <c r="F27" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -14683,7 +15125,7 @@
       </c>
       <c r="F28" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sprint 6</t>
         </is>
       </c>
     </row>
@@ -14778,7 +15220,7 @@
       </c>
       <c r="F31" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -14811,7 +15253,7 @@
       </c>
       <c r="F32" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -14842,7 +15284,7 @@
       </c>
       <c r="F33" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -14968,7 +15410,7 @@
       </c>
       <c r="F37" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -15000,7 +15442,7 @@
       </c>
       <c r="F38" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -15031,7 +15473,7 @@
       </c>
       <c r="F39" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -15095,7 +15537,7 @@
       </c>
       <c r="F41" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -15126,7 +15568,7 @@
       </c>
       <c r="F42" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -15158,7 +15600,7 @@
       </c>
       <c r="F43" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -15189,7 +15631,7 @@
       </c>
       <c r="F44" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -15221,7 +15663,7 @@
       </c>
       <c r="F45" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -15315,7 +15757,7 @@
       </c>
       <c r="F48" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -15346,7 +15788,7 @@
       </c>
       <c r="F49" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>

--- a/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S1.xlsx
+++ b/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S1.xlsx
@@ -5004,11 +5004,17 @@
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I51" s="11" t="n"/>
-      <c r="J51" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I51" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J51" s="20" t="inlineStr">
+        <is>
+          <t>Validado con la Product Owner (registrado el 27-09-2026 por indicación de Bryan Chávez).</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="27.6" customHeight="1" s="24">
       <c r="A52" s="11" t="inlineStr">
@@ -6310,11 +6316,17 @@
       </c>
       <c r="H80" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I80" s="11" t="n"/>
-      <c r="J80" s="20" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I80" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J80" s="20" t="inlineStr">
+        <is>
+          <t>Validado con la Product Owner (registrado el 27-09-2026 por indicación de Bryan Chávez).</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="27.6" customHeight="1" s="24">
       <c r="A81" s="11" t="inlineStr">
